--- a/docs/pie-chart/PieChart_仕様一覧.xlsx
+++ b/docs/pie-chart/PieChart_仕様一覧.xlsx
@@ -12,15 +12,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト仕様" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入出力定義'!$A$4:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'入出力定義'!$A$4:$E$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'入出力定義'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'入出力定義'!$A$1:$E$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLI・設定'!$A$4:$E$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'入出力定義'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CLI・設定'!$A$4:$E$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'CLI・設定'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'CLI・設定'!$A$1:$E$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テスト仕様'!$A$4:$E$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'CLI・設定'!$A$1:$E$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テスト仕様'!$A$4:$E$15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'テスト仕様'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'テスト仕様'!$A$1:$E$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'テスト仕様'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -546,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Graph2 仕様一覧（入出力 / CLI・設定 / テスト）</t>
+          <t>PieChart 仕様一覧（入出力 / CLI・設定 / テスト）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>対象: 円グラフ SVG レンダラ Graph2 ・ 版 1.0 ・ 出典: graph2/ 実装コード・テスト（DB なし）</t>
+          <t>対象: 円グラフ SVG レンダラ PieChart ・ 版 1.0 ・ 出典: pie-chart/ 実装コード・テスト</t>
         </is>
       </c>
     </row>
@@ -753,22 +753,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>入力</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>SVG文字列</t>
+          <t>DB(SQL Server)</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>600×450px 固定</t>
+          <t>単一SELECT文の結果セット</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>スライスpath・ラベル・リーダー線・WOFF2埋込フォント</t>
+          <t>--sql。先頭2列 or --name-col/--value-col。Windows統合認証・msnodesqlv8隔離</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>テキスト要素</t>
+          <t>SVG文字列</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>&lt;text&gt;（実テキスト）</t>
+          <t>600×450px 固定</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>ラベルとパーセンテージは後から検索可能</t>
+          <t>スライスpath・ラベル・リーダー線・WOFF2埋込フォント</t>
         </is>
       </c>
     </row>
@@ -808,22 +808,47 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
+          <t>テキスト要素</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>&lt;text&gt;（実テキスト）</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>ラベルとパーセンテージは後から検索可能</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>出力</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
           <t>リーダー線</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>&lt;path&gt;（引出線）</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>決定的シリアライズ（同一入力→同一バイト）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E13"/>
+  <autoFilter ref="A4:E14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -839,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -852,14 +877,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Graph2 仕様一覧（入出力 / CLI・設定 / テスト）</t>
+          <t>PieChart 仕様一覧（入出力 / CLI・設定 / テスト）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>対象: 円グラフ SVG レンダラ Graph2 ・ 版 1.0 ・ 出典: graph2/ 実装コード・テスト（DB なし）</t>
+          <t>対象: 円グラフ SVG レンダラ PieChart ・ 版 1.0 ・ 出典: pie-chart/ 実装コード・テスト</t>
         </is>
       </c>
     </row>
@@ -1048,17 +1073,13 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>--font-weight</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>400 | 700</t>
-        </is>
-      </c>
+          <t>--sql</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>フォントウェイト切替</t>
+          <t>SQL Serverへ単一SELECT。結果セットから取り込み</t>
         </is>
       </c>
     </row>
@@ -1073,17 +1094,17 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>--stroke-ratio</t>
+          <t>--db-server / --db-name</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>env DB_SERVER / DB_NAME</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>faux-bold のストローク調整</t>
+          <t>接続先（既定 localhost / env）。Windows統合認証固定</t>
         </is>
       </c>
     </row>
@@ -1098,13 +1119,17 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>--output-file / --output-dir</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr"/>
+          <t>--name-col / --value-col</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>先頭2列</t>
+        </is>
+      </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>出力先指定</t>
+          <t>両指定で列名解決。無指定は先頭2列</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1139,22 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>設定</t>
+          <t>オプション</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>svgWidthPx / svgHeightPx</t>
+          <t>--font-weight</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>600 / 450</t>
+          <t>400 | 700</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>SVG寸法（固定）</t>
+          <t>フォントウェイト切替</t>
         </is>
       </c>
     </row>
@@ -1139,22 +1164,22 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>設定</t>
+          <t>オプション</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>pieHeightRatio</t>
+          <t>--stroke-ratio</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>直径 = 450 × 0.7 = 315px</t>
+          <t>faux-bold のストローク調整</t>
         </is>
       </c>
     </row>
@@ -1164,22 +1189,18 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>設定</t>
+          <t>オプション</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>baselineFontSize</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>--output-file / --output-dir</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>基準フォントサイズ</t>
+          <t>出力先指定</t>
         </is>
       </c>
     </row>
@@ -1194,17 +1215,17 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>fontSize</t>
+          <t>svgWidthPx / svgHeightPx</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>600 / 450</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>実描画。40 × 0.68 ≈ 27.2px</t>
+          <t>SVG寸法（固定）</t>
         </is>
       </c>
     </row>
@@ -1219,17 +1240,17 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>labelRadius</t>
+          <t>pieHeightRatio</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>ラベル配置半径倍率</t>
+          <t>直径 = 450 × 0.7 = 315px</t>
         </is>
       </c>
     </row>
@@ -1244,17 +1265,17 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>startangle</t>
+          <t>baselineFontSize</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>12時を0°に</t>
+          <t>基準フォントサイズ</t>
         </is>
       </c>
     </row>
@@ -1269,17 +1290,17 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>minGap</t>
+          <t>fontSize</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>ラベル最小間隔</t>
+          <t>実描画。40 × 0.68 ≈ 27.2px</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1315,17 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>smallSliceThreshold</t>
+          <t>labelRadius</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>小スライス判定（%）</t>
+          <t>ラベル配置半径倍率</t>
         </is>
       </c>
     </row>
@@ -1319,22 +1340,97 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
+          <t>startangle</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>12時を0°に</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>設定</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>minGap</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>ラベル最小間隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>設定</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>smallSliceThreshold</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>小スライス判定（%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>設定</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
           <t>denseCountThreshold</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>密判定のスライス数閾値</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E23"/>
+  <autoFilter ref="A4:E26"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -1350,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1363,14 +1459,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Graph2 仕様一覧（入出力 / CLI・設定 / テスト）</t>
+          <t>PieChart 仕様一覧（入出力 / CLI・設定 / テスト）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>対象: 円グラフ SVG レンダラ Graph2 ・ 版 1.0 ・ 出典: graph2/ 実装コード・テスト（DB なし）</t>
+          <t>対象: 円グラフ SVG レンダラ PieChart ・ 版 1.0 ・ 出典: pie-chart/ 実装コード・テスト</t>
         </is>
       </c>
     </row>
@@ -1632,32 +1728,57 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
+          <t>verify_consistency.ts</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>採点判断（scorer）↔ emit SVG の一致検証</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>scorer↔emit が乖離なし</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
           <t>batch + out/_baseline</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>決定的出力の byte-diff</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>baseline と完全一致</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E14"/>
+  <autoFilter ref="A4:E15"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E14">
+  <conditionalFormatting sqref="E5:E15">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"合格"</formula>
     </cfRule>
